--- a/data/trans_dic/IP44C$ninguna_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$ninguna_2023-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que no han tenido retrasos en pagos</t>
+          <t>Adultos que no han tenido retrasos en pagos (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>82,13; 91,86</t>
+          <t>82,23; 92,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>84,95; 94,44</t>
+          <t>85,41; 94,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85,5; 92,41</t>
+          <t>85,85; 92,43</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>83,99; 91,76</t>
+          <t>84,0; 91,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>78,08; 86,93</t>
+          <t>77,65; 86,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81,61; 87,96</t>
+          <t>82,0; 87,79</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41,44; 87,81</t>
+          <t>42,73; 88,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82,15; 91,28</t>
+          <t>82,49; 91,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62,7; 88,04</t>
+          <t>59,29; 88,35</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>70,91; 82,7</t>
+          <t>71,06; 82,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>77,03; 87,86</t>
+          <t>77,53; 87,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75,99; 83,54</t>
+          <t>76,21; 83,98</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>69,67; 85,76</t>
+          <t>69,35; 85,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>82,95; 87,47</t>
+          <t>82,9; 87,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77,11; 85,81</t>
+          <t>77,02; 85,75</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que no han tenido retrasos en pagos (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>102179</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>123422</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>225600</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>95646; 107082</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>116426; 128570</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>216874; 233510</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>519</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>165315</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>207496</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>372811</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>156967; 171216</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>195054; 217261</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>359199; 384583</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>139400</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>156701</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>296101</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>80304; 166376</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>147906; 163961</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>217734; 324458</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>124179</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>147545</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>271724</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>114392; 132508</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>137421; 155176</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>257755; 284030</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>784</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1591</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>531074</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>635163</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1166237</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>452247; 560631</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>616796; 652291</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1075361; 1197165</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP44C$ninguna_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$ninguna_2023-Habitat-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>82,23; 92,06</t>
+          <t>82,48; 92,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85,41; 94,32</t>
+          <t>85,5; 94,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85,85; 92,43</t>
+          <t>85,41; 92,11</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>84,0; 91,63</t>
+          <t>84,3; 91,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>77,65; 86,49</t>
+          <t>77,92; 86,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,0; 87,79</t>
+          <t>81,92; 87,89</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>42,73; 88,52</t>
+          <t>45,7; 88,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82,49; 91,45</t>
+          <t>82,22; 91,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59,29; 88,35</t>
+          <t>54,86; 88,09</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>71,06; 82,31</t>
+          <t>71,22; 82,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>77,53; 87,55</t>
+          <t>77,76; 87,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76,21; 83,98</t>
+          <t>76,39; 83,91</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>69,35; 85,97</t>
+          <t>65,74; 85,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>82,9; 87,67</t>
+          <t>82,89; 87,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77,02; 85,75</t>
+          <t>77,74; 85,92</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>95646; 107082</t>
+          <t>95936; 107096</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>116426; 128570</t>
+          <t>116550; 128698</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>216874; 233510</t>
+          <t>215768; 232693</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>156967; 171216</t>
+          <t>157525; 171888</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>195054; 217261</t>
+          <t>195739; 217683</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>359199; 384583</t>
+          <t>358873; 385010</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>80304; 166376</t>
+          <t>85891; 165400</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>147906; 163961</t>
+          <t>147421; 164161</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>217734; 324458</t>
+          <t>201484; 323524</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>114392; 132508</t>
+          <t>114649; 133465</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>137421; 155176</t>
+          <t>137827; 155341</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>257755; 284030</t>
+          <t>258363; 283809</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>452247; 560631</t>
+          <t>428690; 559367</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>616796; 652291</t>
+          <t>616709; 652008</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1075361; 1197165</t>
+          <t>1085398; 1199550</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$ninguna_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$ninguna_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,03%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>82,48; 92,07</t>
+          <t>84,16; 94,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85,5; 94,41</t>
+          <t>81,96; 92,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85,41; 92,11</t>
+          <t>85,09; 92,15</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>84,72%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>84,3; 91,99</t>
+          <t>77,12; 86,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>77,92; 86,66</t>
+          <t>83,8; 91,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81,92; 87,89</t>
+          <t>81,34; 87,66</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>86,76%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>45,7; 88,0</t>
+          <t>82,71; 91,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82,22; 91,56</t>
+          <t>78,6; 90,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>54,86; 88,09</t>
+          <t>82,96; 90,01</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>79,43%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>71,22; 82,9</t>
+          <t>76,32; 87,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>77,76; 87,64</t>
+          <t>70,09; 81,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76,39; 83,91</t>
+          <t>74,84; 82,75</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>84,69%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>65,74; 85,78</t>
+          <t>82,46; 87,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>82,89; 87,63</t>
+          <t>81,19; 86,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77,74; 85,92</t>
+          <t>82,7; 86,26</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>169</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>102179</t>
+          <t>109733</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>123422</t>
+          <t>105830</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>225600</t>
+          <t>215563</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>95936; 107096</t>
+          <t>102520; 114538</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>116550; 128698</t>
+          <t>98618; 110797</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>215768; 232693</t>
+          <t>206017; 223107</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>239</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>165315</t>
+          <t>191090</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>207496</t>
+          <t>159961</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>372811</t>
+          <t>351052</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>157525; 171888</t>
+          <t>180076; 201490</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>195739; 217683</t>
+          <t>151571; 166105</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>358873; 385010</t>
+          <t>337057; 363237</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>194</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>139400</t>
+          <t>142066</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>156701</t>
+          <t>132602</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>296101</t>
+          <t>274669</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>85891; 165400</t>
+          <t>133856; 148140</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>147421; 164161</t>
+          <t>121619; 139615</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>201484; 323524</t>
+          <t>262635; 284947</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>182</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>124179</t>
+          <t>136959</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>147545</t>
+          <t>122712</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>271724</t>
+          <t>259671</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>114649; 133465</t>
+          <t>126636; 145191</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>137827; 155341</t>
+          <t>112833; 131900</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>258363; 283809</t>
+          <t>244662; 270521</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>784</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>807</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>531074</t>
+          <t>579849</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>635163</t>
+          <t>521106</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1166237</t>
+          <t>1100955</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>428690; 559367</t>
+          <t>563302; 595555</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>616709; 652008</t>
+          <t>500868; 534917</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1085398; 1199550</t>
+          <t>1075138; 1121333</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$ninguna_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$ninguna_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Adultos que no han tenido retrasos en pagos (tasa de respuesta: 97,81%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>90,09%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>87,96%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>89,03%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>84,16; 94,03</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>81,96; 92,09</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>85,09; 92,15</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>81,83%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>88,44%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>84,72%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>77,12; 86,29</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>83,8; 91,84</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>81,34; 87,66</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>87,78%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>85,7%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>86,76%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>82,71; 91,53</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>78,6; 90,23</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>82,96; 90,01</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>82,54%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>76,22%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>79,43%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>76,32; 87,5</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>70,09; 81,93</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>74,84; 82,75</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>84,89%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>84,47%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>84,69%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>82,46; 87,19</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>81,19; 86,71</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>82,7; 86,26</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.9008663693169917</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.8795853777719155</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.8902913791768691</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>109733</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>105830</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>215563</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.8416488876247644</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.8196431749191181</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.8508684504715226</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>102520; 114538</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>98618; 110797</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>206017; 223107</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.9403172771883201</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.9208708450485933</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.9214509561282311</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.818345801788705</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.8844090058358689</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.8471812833205358</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>191090</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>159961</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>351052</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.7711770902501359</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.838019225299492</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.8134075593405434</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>180076; 201490</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>151571; 166105</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>337057; 363237</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.8628845494741392</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.9183777157310601</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.8765847790213047</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.8778108532852951</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.8570060772476493</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.8676422217981276</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>142066</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>132602</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>274669</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.827083205184272</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.7860224196846718</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.8296280685840154</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>133856; 148140</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>121619; 139615</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>262635; 284947</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.9153446699644308</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.9023336042071128</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.9001089143224936</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.8254149819384835</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.7622276827058777</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.7942984885511626</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>136959</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>122712</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>259671</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.7631975550273692</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.7008660057050889</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.7483867213623587</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>126636; 145191</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>112833; 131900</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>244662; 270521</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.8750219099860032</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.8193001771907633</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.8274853951741736</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>807</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>784</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1591</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.8488669378034289</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.8447100853252083</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.8468943225906154</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>579849</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>521106</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1100955</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.8246427522928514</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.8119040574921438</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.8270347586994315</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>563302; 595555</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>500868; 534917</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1075138; 1121333</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.8718596627219037</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.8670979684719515</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.8625700402158752</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que no han tenido retrasos en pagos (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>148</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>169</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>109733</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>105830</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>215563</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>102520</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>98618</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>206017</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>114538</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>110797</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>223107</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>280</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>239</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>191090</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>159961</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>351052</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>180076</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>151571</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>337057</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>201490</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>166105</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>363237</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>184</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>194</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>142066</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>132602</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>274669</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>133856</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>121619</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>262635</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>148140</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>139615</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>284947</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>195</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>182</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>136959</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>122712</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>259671</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>126636</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>112833</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>244662</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>145191</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>131900</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>270521</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>807</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>784</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>579849</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>521106</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1100955</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>563302</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>500868</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>1075138</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>595555</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>534917</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>1121333</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>